--- a/docs/Functions List.xlsx
+++ b/docs/Functions List.xlsx
@@ -128,7 +128,7 @@
     <t>Register</t>
   </si>
   <si>
-    <t>Khách hàng đăng ký tài khoản (username, email, số điện thoại) với mật khẩu mặc định là 123456.</t>
+    <t>Khách hàng đăng ký tài khoản (username, email, số điện thoại) với mật khẩu mặc định do hệ thống cấu hình (RIMS_DEFAULT_PASSWORD), và bị bắt đổi ngay ở lần đăng nhập đầu.</t>
   </si>
   <si>
     <t>Forgot Password</t>
